--- a/backend/data/financials_by_company/002707.SZ.xlsx
+++ b/backend/data/financials_by_company/002707.SZ.xlsx
@@ -4323,10 +4323,8 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100125</t>
-        </is>
+      <c r="D2" t="n">
+        <v>100125</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4543,7 +4541,7 @@
         <v>-2008094</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>0.2</v>
@@ -4818,7 +4816,7 @@
         <v>1651492800</v>
       </c>
       <c r="EN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO2" t="n">
         <v>0.2</v>
